--- a/mode_docx_gen/pmi_lodzt/lot_modes/ЛО Т_12.xlsx
+++ b/mode_docx_gen/pmi_lodzt/lot_modes/ЛО Т_12.xlsx
@@ -677,14 +677,14 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -764,8 +764,8 @@
       <c r="AG2" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" t="n">
-        <v>0</v>
+      <c r="AH2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1116,8 +1116,8 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
+      <c r="J2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1505,9 +1505,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1525,9 +1525,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1540,9 +1540,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1550,14 +1550,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1695,9 +1695,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1735,9 +1735,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AU2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
